--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">_articlesToRemove</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">a ,an </t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">_articlesToRemove</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">a ,an </t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">_articlesToRemove</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">a ,an </t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">_articlesToRemove</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">a ,an </t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">_articlesToRemove</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">a ,an </t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/List.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="488">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -878,6 +878,21 @@
   </si>
   <si>
     <t xml:space="preserve">訓練する技能の選択,,,技能の候補,消費プラチナ硬貨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wSkyTravel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좌표 선택,,,목적 좌표,소모 티켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a coordination to move,,,Coordination,Ticket Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">座標の選択,,,目的の座標,消費チケット</t>
   </si>
   <si>
     <t xml:space="preserve">wCraft</t>
@@ -1700,7 +1715,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="16.15"/>
@@ -2992,24 +3007,24 @@
         <v>295</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="C71" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>89</v>
@@ -3018,21 +3033,21 @@
         <v>242</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>304</v>
+        <v>89</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>242</v>
@@ -3052,59 +3067,59 @@
         <v>308</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>89</v>
+        <v>309</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>313</v>
+        <v>89</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D76" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="F76" s="0" t="s">
         <v>316</v>
-      </c>
-      <c r="E76" s="0" t="s">
-        <v>317</v>
-      </c>
-      <c r="F76" s="0" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3112,24 +3127,24 @@
         <v>319</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>89</v>
@@ -3138,18 +3153,18 @@
         <v>242</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>89</v>
@@ -3158,435 +3173,435 @@
         <v>242</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>242</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>264</v>
+        <v>10</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>242</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>72</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>72</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>233</v>
+        <v>72</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>233</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>89</v>
+        <v>233</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>89</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>264</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>54</v>
+        <v>264</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>428</v>
+        <v>54</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>429</v>
@@ -3603,75 +3618,78 @@
         <v>432</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>224</v>
+        <v>291</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>433</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>449</v>
+        <v>26</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>450</v>
@@ -3722,24 +3740,24 @@
         <v>463</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>469</v>
@@ -3762,78 +3780,95 @@
         <v>474</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
